--- a/docs/meals_reimbursment.xlsx
+++ b/docs/meals_reimbursment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fonse\_CODDING\prt_welfare\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fonse\_CODDING\sigcp\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B48F4A5-1506-493F-B374-6B6E82AD6EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32234848-19BF-47BB-8CC3-1884F2FD7251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CF93EE5-D891-4A27-B513-3B9F6F237990}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{7CF93EE5-D891-4A27-B513-3B9F6F237990}"/>
   </bookViews>
   <sheets>
     <sheet name="F1" sheetId="1" r:id="rId1"/>
@@ -95,13 +95,13 @@
     <t>Portugal</t>
   </si>
   <si>
-    <t>OF-5 CARLOS MACHADO certify that I have verified the total number of meals for each personal and that is within the limits imposed by SOP 80-007 (20 meals per month)</t>
+    <t>SNR certify that I have verified the total number of meals for each personal and that is within the limits imposed by SOP 80-007 (20 meals per month)</t>
   </si>
   <si>
-    <t>OF-5 CARLOS MACHADO certify that I have verified that each personal did not eat at DFAC or in service meals (MRE) for the meals which I am requesting reimbursment for</t>
+    <t>SNR certify that a service note has been made and signed by COS for each national cohesion activity and brunch cohesion activity</t>
   </si>
   <si>
-    <t>OF-5 CARLOS MACHADO certify that a service note has been made and signed by COS for each national cohesion activity and brunch cohesion activity</t>
+    <t>SNR certify that I have verified that each personal did not eat at DFAC or in service meals (MRE) for the meals which I am requesting reimbursment for</t>
   </si>
 </sst>
 </file>
@@ -257,17 +257,17 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -284,11 +284,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,40 +702,40 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -744,8 +744,8 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -754,8 +754,8 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -764,8 +764,8 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
@@ -774,8 +774,8 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
@@ -784,8 +784,8 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -794,8 +794,8 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
@@ -804,8 +804,8 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
@@ -814,8 +814,8 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
@@ -824,8 +824,8 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -834,8 +834,8 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
@@ -844,8 +844,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
@@ -854,8 +854,8 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
@@ -864,8 +864,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
@@ -874,8 +874,8 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="10"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
@@ -884,56 +884,56 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="13"/>
       <c r="G24" s="14"/>
       <c r="H24" s="15"/>
     </row>
     <row r="26" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -955,12 +955,12 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -977,12 +977,12 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:F8"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B19:B23">
@@ -1044,40 +1044,40 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -1086,8 +1086,8 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -1096,8 +1096,8 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -1106,8 +1106,8 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
@@ -1116,8 +1116,8 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
@@ -1126,8 +1126,8 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -1136,8 +1136,8 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
@@ -1146,8 +1146,8 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
@@ -1156,8 +1156,8 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
@@ -1166,8 +1166,8 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -1176,8 +1176,8 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
@@ -1186,8 +1186,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
@@ -1196,8 +1196,8 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
@@ -1206,8 +1206,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
@@ -1216,8 +1216,8 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="10"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
@@ -1226,56 +1226,56 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="13"/>
       <c r="G24" s="14"/>
       <c r="H24" s="15"/>
     </row>
     <row r="26" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -1297,6 +1297,26 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="G21:H21"/>
@@ -1305,26 +1325,6 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="B19:B23">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
@@ -1385,40 +1385,40 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -1427,8 +1427,8 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -1437,8 +1437,8 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -1447,8 +1447,8 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
@@ -1457,8 +1457,8 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
@@ -1467,8 +1467,8 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -1477,8 +1477,8 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
@@ -1487,8 +1487,8 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
@@ -1497,8 +1497,8 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
@@ -1507,8 +1507,8 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -1517,8 +1517,8 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
@@ -1527,8 +1527,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
@@ -1537,8 +1537,8 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
@@ -1547,8 +1547,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
@@ -1557,8 +1557,8 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="10"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
@@ -1567,56 +1567,56 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="13"/>
       <c r="G24" s="14"/>
       <c r="H24" s="15"/>
     </row>
     <row r="26" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -1638,6 +1638,26 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="G21:H21"/>
@@ -1646,26 +1666,6 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="B19:B23">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
@@ -1726,40 +1726,40 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -1768,8 +1768,8 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -1778,8 +1778,8 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -1788,8 +1788,8 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
@@ -1798,8 +1798,8 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
@@ -1808,8 +1808,8 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -1818,8 +1818,8 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
@@ -1828,8 +1828,8 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
@@ -1838,8 +1838,8 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
@@ -1848,8 +1848,8 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -1858,8 +1858,8 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
@@ -1868,8 +1868,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
@@ -1878,8 +1878,8 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
@@ -1888,8 +1888,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
@@ -1898,8 +1898,8 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="10"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
@@ -1908,56 +1908,56 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="13"/>
       <c r="G24" s="14"/>
       <c r="H24" s="15"/>
     </row>
     <row r="26" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -1979,6 +1979,26 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="G21:H21"/>
@@ -1987,26 +2007,6 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="B19:B23">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
@@ -2067,40 +2067,40 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
@@ -2109,8 +2109,8 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
@@ -2119,8 +2119,8 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -2129,8 +2129,8 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="10"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
@@ -2139,8 +2139,8 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
@@ -2149,8 +2149,8 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -2159,8 +2159,8 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
@@ -2169,8 +2169,8 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
@@ -2179,8 +2179,8 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
@@ -2189,8 +2189,8 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="10"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
@@ -2199,8 +2199,8 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
@@ -2209,8 +2209,8 @@
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
@@ -2219,8 +2219,8 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="18"/>
     </row>
     <row r="21" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
@@ -2229,8 +2229,8 @@
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="10"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
@@ -2239,8 +2239,8 @@
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="10"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
@@ -2249,56 +2249,56 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="13"/>
       <c r="G24" s="14"/>
       <c r="H24" s="15"/>
     </row>
     <row r="26" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-    </row>
-    <row r="28" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -2320,6 +2320,26 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="G21:H21"/>
@@ -2328,26 +2348,6 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="B19:B23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
